--- a/artfynd/A 1342-2026 artfynd.xlsx
+++ b/artfynd/A 1342-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125837720</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1342-2026 artfynd.xlsx
+++ b/artfynd/A 1342-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125837720</v>
+        <v>127851005</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102975</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,26 +713,29 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Olsbacka, Dlr</t>
+          <t>E 16;50, 784 77 Ornäs, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529469</v>
+        <v>530017</v>
       </c>
       <c r="R2" t="n">
-        <v>6710706</v>
+        <v>6710592</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,7 +744,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -751,27 +754,27 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Aspeboda</t>
+          <t>Torsång</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,15 +789,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Danielsson</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Danielsson, Olle Valseth Danielsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1342-2026 artfynd.xlsx
+++ b/artfynd/A 1342-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,8 +807,16 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127851005</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>